--- a/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0004.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0004.xlsx
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Có lẽ cậu đã đoán ra rồi. {PlayerName} chính là người hùng đã chiến đấu bên cạnh Sentinel của chúng ta trong những ngày đầu ở Jinzhou. {Male=Anh ấy;Female=Cô ấy} cũng chính là vị khách bí ẩn được nhắc đến trong truyền thuyết về Núi Firmament.</t>
+          <t>Có lẽ cậu đã đoán ra rồi. {PlayerName} chính là người hùng đã chiến đấu bên cạnh Sentinel của chúng ta trong những ngày đầu ở Jinzhou. {Male=He;Female=She} cũng chính là vị khách bí ẩn được nhắc đến trong truyền thuyết về Núi Firmament.</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
 Memo 0x002: Phát hiện đối tượng bất ngờ. Đối tượng này tỏ ra thận trọng, quanh quẩn gần trại. Được đánh giá tạm thời là Discord cấp Elite hoặc cao hơn. Đánh giá sơ bộ cho thấy đối tượng này không gây nguy hiểm ngay lập tức cho thí nghiệm. ■■ ra lệnh cho Đội ■ bắt giữ đối tượng này để sử dụng tiềm năng sau khi thí nghiệm thành công (phần sau không đọc được).
 Ghi chép Trình tự 03-29: Phát hiện nhân vật không xác định gần trại, nhưng đã bỏ chạy khi tiếp xúc với đối tượng bất ngờ. Được cho là cư dân Hongzhen. ■■ ra lệnh tăng tần suất thí nghiệm để hoàn thành trước khi Hongzhen phản ứng.
 ■■■■■■■: Đạt được thành công bước đầu. Kỹ thuật ■■■■■■■■ các mẫu có thể nhân rộng. ■■ đề xuất khởi động kế hoạch bắt giữ đối tượng bất ngờ càng sớm càng tốt. Đội ■ cho rằng rủi ro quá cao nhưng bị bác bỏ. (Phần còn lại không đọc được.)
-(Nửa sau của tờ ghi chú được viết vội vàng, Dodget chữ lộn xộn, khó đọc.)
+(Nửa sau của tờ ghi chú được viết vội vàng, nét chữ lộn xộn, khó đọc.)
 Bắt giữ thất bại... nổi giận... mối đe dọa cấp Elite... Bỏ trại, di chuyển đến Địa điểm 2... CHẠY... (Đoạn cuối hoàn toàn bị lem mực.)</t>
         </is>
       </c>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Cụ cố của ông nội Zou là hậu duệ của những cư dân đầu tiên ở Hồng Trấn. Từ nhỏ, ông đã nghe kể về núi Cương Trực. Gần đây, nghe tin Bà Quan đã giải quyết được khủng hoảng, ông quyết định đến đây để tìm hiểu thêm về cội nguồn của mình.</t>
+          <t>Cụ cố của ông nội Zou là hậu duệ của những cư dân đầu tiên ở Hongzhen. Từ nhỏ, ông đã nghe kể về núi Cương Trực. Gần đây, nghe tin Bà Quan đã giải quyết được khủng hoảng, ông quyết định đến đây để tìm hiểu thêm về cội nguồn của mình.</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Núi Firmament từng gặp phải những Rối Loạn Thời Gian do lịch sử đầy biến động. Nhưng nhờ Quan Phủ Jinhsi và Rover, những rối loạn đó đã được giải quyết. Ít nhất, chúng ta đã hy vọng như vậy.</t>
+          <t>Núi Firmament từng gặp phải những Rối Loạn Thời Gian do lịch sử đầy biến động. Nhưng nhờ Quan Phủ Jinhsi và Vận Mệnh Giả, những rối loạn đó đã được giải quyết. Ít nhất, chúng ta đã hy vọng như vậy.</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Vậy là trên núi vẫn còn những Echo chưa được xử lý. Và thật không may, Wuli đã vô tình gặp phải một cái, nhầm tưởng đó là phương thuốc huyền thoại hắn tìm kiếm.</t>
+          <t>Vậy là trên núi vẫn còn những Tổ Tacet chưa được xử lý. Và thật không may, Wuli đã vô tình gặp phải một cái, nhầm tưởng đó là phương thuốc huyền thoại hắn tìm kiếm.</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Hắn hoàn toàn tin vào phát hiện của mình, và bằng cách nào đó, chỉ trong nửa ngày đã gặp phải những Rối Loạn Thời Gian. Còn nữa… khi ta tra hỏi, hắn Dodge.</t>
+          <t>Hắn hoàn toàn tin vào phát hiện của mình, và bằng cách nào đó, chỉ trong nửa ngày đã gặp phải những Rối Loạn Thời Gian. Còn nữa… khi ta tra hỏi, hắn né tránh.</t>
         </is>
       </c>
     </row>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Fuling đã chấp nhận cái chết đang đến gần. Cô không tin vào những truyền thuyết về "bất tử". Thay vào đó, cô chỉ muốn tận dụng thời gian còn lại để hoàn thành ước mơ của mình và Wuli.</t>
+          <t>Phúc Linh đã chấp nhận cái chết đang đến gần. Cô không tin vào những truyền thuyết về "bất tử". Thay vào đó, cô chỉ muốn tận dụng thời gian còn lại để hoàn thành ước mơ của mình và Wuli.</t>
         </is>
       </c>
     </row>
@@ -6396,7 +6396,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Khoan, cô ta thực sự làm được gì đáng kể trong thời gian ở Jinzhou không? Hay bà Đại Nhân chỉ bị mấy lời đường mật của cô ta lừa mà cho qua thôi?</t>
+          <t>Đợi đã, cô ta thực sự làm được gì đáng kể trong thời gian ở Jinzhou không? Hay bà Đại Nhân chỉ bị mấy lời đường mật của cô ta lừa mà cho qua thôi?</t>
         </is>
       </c>
     </row>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Chắc hẳn bà ta sợ {Male=hắn;Female=cô ấy} lại quá thân thiết với Quý Bà Thẩm Phán và phá hỏng kế hoạch của mình... Thật là một mụ đàn bà nham hiểm! May mà vị khách kia là một cao thủ, và {Male=hắn;Female:cô ấy} đã chạy thoát an toàn.</t>
+          <t>Chắc hẳn bà ta sợ {Male=he;Female=she} lại quá thân thiết với Quý Bà Thẩm Phán và phá hỏng kế hoạch của mình... Thật là một mụ đàn bà nham hiểm! May mà vị khách kia là một cao thủ, và {Male=he;Female=she} đã chạy thoát an toàn.</t>
         </is>
       </c>
     </row>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Là đệ tử của Master Xuanmiao, cô tinh thông nghệ thuật chính trị và ngoại giao. Những chuyến du hành đã đưa cô đi khắp bốn biển, và với tư cách Tổng thư ký, cô đã khiến mọi kẻ qua đường phải kính nể!</t>
+          <t>Là đệ tử của Sư phụ Xuanmiao, cô tinh thông nghệ thuật chính trị và ngoại giao. Những chuyến du hành đã đưa cô đi khắp bốn biển, và với tư cách Tổng thư ký, cô đã khiến mọi kẻ qua đường phải kính nể!</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Tôi không khỏi ghen tị. Ước gì tôi có thể nói chuyện với cô ấy như cậu đã làm, nhưng cô ấy từ chối phỏng vấn với Pioneer Association. Hơn nữa, tôi cũng chẳng nghĩ chúng tôi có điểm chung gì mà nói cả.</t>
+          <t>Tôi không khỏi ghen tị. Ước gì tôi có thể nói chuyện với cô ấy như cậu đã làm, nhưng cô ấy từ chối phỏng vấn với Hiệp Hội Tiên Phong. Hơn nữa, tôi cũng chẳng nghĩ chúng tôi có điểm chung gì mà nói cả.</t>
         </is>
       </c>
     </row>
@@ -6916,7 +6916,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Cảm ơn sự hỗ trợ của các cậu. Đội Midnight Rangers đã bắt giữ thành công tất cả thành viên Fractsidus còn lại trên núi, và hiệu ứng của Sự Rối Loạn Thời Gian đã biến mất.</t>
+          <t>Cảm ơn sự hỗ trợ của các cậu. Đội Kỵ Sĩ Bóng Đêm đã bắt giữ thành công tất cả thành viên Fractsidus còn lại trên núi, và hiệu ứng của Sự Rối Loạn Thời Gian đã biến mất.</t>
         </is>
       </c>
     </row>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Until the day... khi tôi không còn cầm nổi cây bút. Tôi đã nói chuyện với mọi người ở nhà xuất bản, và họ sẵn lòng để tôi tiếp tục vẽ cho họ.</t>
+          <t>Cho đến ngày... khi tôi không còn cầm nổi cây bút. Tôi đã nói chuyện với mọi người ở nhà xuất bản, và họ sẵn lòng để tôi tiếp tục vẽ cho họ.</t>
         </is>
       </c>
     </row>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Trong một đợt bùng phát Tacet Discord, sư phụ của ta đã được người đó cứu mạng. {Male=Hắn;Female=Nàng} toát ra một nguồn năng lượng kỳ lạ và luôn khó nắm bắt. Sư phụ ta đã lục tìm trong các văn bản cổ và phát hiện ra dấu vết của {Male=hắn;Female=nàng} trong những trang sử bị lãng quên từ lâu.</t>
+          <t>Trong một đợt bùng phát Tacet Discord, sư phụ của ta đã được người đó cứu mạng. {Male=his;Female=her} toát ra một nguồn năng lượng kỳ lạ và luôn khó nắm bắt. Sư phụ ta đã lục tìm trong các văn bản cổ và phát hiện ra dấu vết của {Male=his;Female=her} trong những trang sử bị lãng quên từ lâu.</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Centuries ago, một đạo sĩ tu luyện đã gặp một vị khách bí ẩn trên núi Kiên Cố. Dù cách biệt tuổi tác, họ nhanh chóng trở thành bạn bè và thường xuyên cùng nhau chơi cờ vây.</t>
+          <t>Cách đây hàng thế kỷ, một đạo sĩ tu luyện đã gặp một vị khách bí ẩn trên núi Kiên Cố. Dù cách biệt tuổi tác, họ nhanh chóng trở thành bạn bè và thường xuyên cùng nhau chơi cờ vây.</t>
         </is>
       </c>
     </row>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Grandpa Zou trông tràn đầy sức sống nhỉ? Ông đến đây với một cuốn sách cũ kỹ, rách nát và bảo muốn tìm lại người thân. Nhưng chẳng ai biết ông cả.</t>
+          <t>Ông nội Zou trông tràn đầy sức sống nhỉ? Ông đến đây với một cuốn sách cũ kỹ, rách nát và bảo muốn tìm lại người thân. Nhưng chẳng ai biết ông cả.</t>
         </is>
       </c>
     </row>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Khi gặp Changli ở đình, cô tiết lộ mọi chuyện. Cậu chính là "vị khách mắt vàng" từng chơi Cờ Vây với Master Xuanmiao. Hồi đó, cậu đã tiên đoán thảm họa sẽ giáng xuống Núi Firmament và rời Sonoro để lại kế hoạch dự phòng. Changli thừa nhận dù không lo lắng về tuổi thọ của mình, nhưng cô vẫn cảm thấy buồn khi nghĩ đến việc phải rời bỏ vẻ đẹp của thế gian. Giờ đây, cô muốn được chơi ván Cờ Vây mà cô hằng mong đợi với cậu.</t>
+          <t>Khi gặp Changli ở đình, cô tiết lộ mọi chuyện. Cậu chính là "vị khách mắt vàng" từng chơi Cờ Vây với Sư phụ Xuanmiao. Hồi đó, cậu đã tiên đoán thảm họa sẽ giáng xuống Núi Firmament và rời Sonoro để lại kế hoạch dự phòng. Changli thừa nhận dù không lo lắng về tuổi thọ của mình, nhưng cô vẫn cảm thấy buồn khi nghĩ đến việc phải rời bỏ vẻ đẹp của thế gian. Giờ đây, cô muốn được chơi ván Cờ Vây mà cô hằng mong đợi với cậu.</t>
         </is>
       </c>
     </row>
@@ -9451,7 +9451,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>(Một Quả Cầu Sonoro bị Rối Loạn Thời Gian... Một khi đã bước vào, nguy cơ bị mắc kẹt vĩnh viễn là rất cao. Nếu như sư phụ ta đã lên kế hoạch từ trước...)</t>
+          <t>(Một Sonoro Sphere bị Rối Loạn Thời Gian... Một khi đã bước vào, nguy cơ bị mắc kẹt vĩnh viễn là rất cao. Nếu như sư phụ ta đã lên kế hoạch từ trước...)</t>
         </is>
       </c>
     </row>
@@ -9581,7 +9581,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Ta nghe nói Master Xuanmiao là một bậc hiền nhân thông thái, luôn giúp đỡ mọi người. Người có thể... nhận ta làm đệ tử không? Ta đã tìm người suốt bao lâu nay... Xin người hãy cân nhắc!</t>
+          <t>Ta nghe nói Sư phụ Xuanmiao là một bậc hiền nhân thông thái, luôn giúp đỡ mọi người. Người có thể... nhận ta làm đệ tử không? Ta đã tìm người suốt bao lâu nay... Xin người hãy cân nhắc!</t>
         </is>
       </c>
     </row>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Nó khiến ta nhớ lại lúc Rover từng hấp thụ năng lượng tần số bằng cơ thể mình y như thế. Thế là chúng ta đưa cậu ấy đến Học Viện để Baizhi kiểm tra.</t>
+          <t>Nó khiến tao nhớ lại lúc Rover từng hấp thụ năng lượng tần số bằng cơ thể mình y như thế. Thế là chúng tao đưa cậu ấy đến Học Viện để Baizhi kiểm tra.</t>
         </is>
       </c>
     </row>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Nó có tần số tương đồng với Dư Âm của Tacet Discord. Giống như một Bản Sao được xử lý bởi Data Bank, lưu trữ trong cơ thể cậu thay vì Terminal.</t>
+          <t>Nó có tần số tương đồng với Dư Âm của Tacet Discord. Giống như một Bản Sao được xử lý bởi Ngân Hàng Dữ Liệu, lưu trữ trong cơ thể cậu thay vì Thiết bị đầu cuối.</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Ngoài nhà hàng của Panhua, sinh vật bên trong cậu, bị hấp dẫn bởi mùi thức ăn, bất chợt trồi ra từ Echo trên người cậu. Những thử nghiệm của Baizhi cho thấy năng lượng Threnodian mà nó hấp thụ đã hoàn toàn hòa quyện với cậu, tạo thành một mối cộng sinh bí ẩn, hay còn gọi là Sự Phụ Thuộc Hội Tụ.</t>
+          <t>Ngoài nhà hàng của Panhua, sinh vật bên trong cậu, bị hấp dẫn bởi mùi thức ăn, bất chợt trồi ra từ Tổ Tacet trên người cậu. Những thử nghiệm của Baizhi cho thấy năng lượng Threnodian mà nó hấp thụ đã hoàn toàn hòa quyện với cậu, tạo thành một mối cộng sinh bí ẩn, hay còn gọi là Sự Phụ Thuộc Hội Tụ.</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Cô ấy kể về những Echoes cực kỳ thông minh ở các nước khác, có thể hành động độc lập. Chúng len lỏi vào mọi mặt của đời sống con người, với những khả năng vượt xa trí tưởng tượng của chúng ta.</t>
+          <t>Cô ấy kể về những Echo cực kỳ thông minh ở các nước khác, có thể hành động độc lập. Chúng len lỏi vào mọi mặt của đời sống con người, với những khả năng vượt xa trí tưởng tượng của chúng ta.</t>
         </is>
       </c>
     </row>
@@ -10556,7 +10556,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Những Echoes này hiếm lắm. Cả ta lẫn Baizhi, chuyên gia Ecoacoustics, đều chưa từng tận mắt thấy bao giờ. Nhưng con nhỏ này… có thể là một trong những Echoes ngoại lai đó.</t>
+          <t>Những Echo này hiếm lắm. Cả tao lẫn Baizhi, chuyên gia Ecoacoustics, đều chưa từng tận mắt thấy bao giờ. Nhưng con nhỏ này… có thể là một trong những Echo ngoại lai đó.</t>
         </is>
       </c>
     </row>
@@ -10686,7 +10686,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Nhưng... dù Echoes có thể có ký ức, có lẽ chúng sẽ không nhớ gì trước lần đầu xuất hiện. Không biết trường hợp của đứa nhỏ này có giống vậy không?</t>
+          <t>Nhưng... dù Echo có thể có ký ức, có lẽ chúng sẽ không nhớ gì trước lần đầu xuất hiện. Không biết trường hợp của đứa nhỏ này có giống vậy không?</t>
         </is>
       </c>
     </row>
@@ -10751,7 +10751,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Ngủ à? Seriously? Lâu lắm rồi đấy! Chuyện gì cũng có, đánh nhau cũng có, mà cậu chẳng nghe thấy gì à? Ừ thì... Chất lượng giấc ngủ của cậu đúng là đỉnh.</t>
+          <t>Ngủ à? Thật sao? Lâu lắm rồi đấy! Chuyện gì cũng có, đánh nhau cũng có, mà cậu chẳng nghe thấy gì à? Ừ thì... Chất lượng giấc ngủ của cậu đúng là đỉnh.</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10816,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Echo nhỏ bé và hiếm có này không nhớ gì về nguồn gốc hay những sự kiện ở Norfall Barrens. Bị cuốn hút bởi khái niệm về tên gọi, nó nhờ cậu đặt cho nó một cái tên, vì bản thân nó đã quên mất tên của mình.</t>
+          <t>Tiếng Vọng nhỏ bé và hiếm có này không nhớ gì về nguồn gốc hay những sự kiện ở Norfall Barrens. Bị cuốn hút bởi khái niệm về tên gọi, nó nhờ cậu đặt cho nó một cái tên, vì bản thân nó đã quên mất tên của mình.</t>
         </is>
       </c>
     </row>
@@ -11076,7 +11076,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Tớ đã nghĩ chúng ta có thể tìm ra nguồn gốc của Abby. Dù không dẫn đến những Echoes đặc biệt khác, nhưng ít nhất cũng là điểm khởi đầu để khám phá quá khứ của {PlayerName}. Rồi chúng ta sẽ có thứ để hỏi lại Madam Magistrate và Sentinel.</t>
+          <t>Tớ đã nghĩ chúng ta có thể tìm ra nguồn gốc của Abby. Dù không dẫn đến những Echo đặc biệt khác, nhưng ít nhất cũng là điểm khởi đầu để khám phá quá khứ của {PlayerName}. Rồi chúng ta sẽ có thứ để hỏi lại Madam Magistrate và Sentinel.</t>
         </is>
       </c>
     </row>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Mỗi Echoes đặc biệt đều có một khả năng riêng. Ta có thể so sánh những gì Abby làm được với các bản ghi về Echoes khác để tìm ra nguồn gốc của chúng. Ngoài ra... Có lẽ nhờ sức mạnh của Abby mà {PlayerName} mới đánh bại được Threnodian?</t>
+          <t>Mỗi Echo đặc biệt đều có một khả năng riêng. Ta có thể so sánh những gì Abby làm được với các bản ghi về Echo khác để tìm ra nguồn gốc của chúng. Ngoài ra... Có lẽ nhờ sức mạnh của Abby mà {PlayerName} mới đánh bại được Threnodian?</t>
         </is>
       </c>
     </row>
@@ -11271,7 +11271,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Đúng như ta đoán. Chẳng có gì ở {PlayerName} lại dễ đoán cả... Hmm. Hay là gọi Baizhi, ông Xiangli Yao, cùng tất cả các nhà nghiên cứu ở Jinzhou... không, cả toàn bộ Huanglong nữa. Họ sẽ kiểm tra Abby kỹ càng, rồi...</t>
+          <t>Đúng như tao đoán. Chẳng có gì ở {PlayerName} lại dễ đoán cả... Hmm. Hay là gọi Baizhi, ông Xiangli Yao, cùng tất cả các nhà nghiên cứu ở Jinzhou... không, cả toàn bộ Huanglong nữa. Họ sẽ kiểm tra Abby kỹ càng, rồi...</t>
         </is>
       </c>
     </row>
@@ -12051,7 +12051,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Đừng bảo là Discord... Khoan đã, vừa có tin nhắn... Hình như chúng lại gây rối rồi. Xin lỗi, nhưng tớ phải đi kiểm tra việc này!</t>
+          <t>Đừng bảo là Tacet Discord... Khoan đã, vừa có tin nhắn... Hình như chúng lại gây rối rồi. Xin lỗi, nhưng tớ phải đi kiểm tra việc này!</t>
         </is>
       </c>
     </row>
@@ -12116,7 +12116,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Cô ấy rất tốt bụng. It's just... bọn mình không thân lắm, mà mình cũng không biết phản ứng thế nào với sự thân thiện của cô ấy... Mình không muốn tỏ ra bất lịch sự, nên... nên mình không nỡ từ chối.</t>
+          <t>Cô ấy rất tốt bụng. Chỉ là... bọn mình không thân lắm, mà mình cũng không biết phản ứng thế nào với sự thân thiện của cô ấy... Mình không muốn tỏ ra bất lịch sự, nên... nên mình không nỡ từ chối.</t>
         </is>
       </c>
     </row>
@@ -12246,7 +12246,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Không rõ lắm, nhưng lúc chạy trốn, tớ nghe thấy cô ấy hét lên với lũ quái vật, kiểu như "Stop! Đừng làm thế!"... Có lẽ cô ấy đang cố ngăn chúng làm hại mọi người.</t>
+          <t>Không rõ lắm, nhưng lúc chạy trốn, tớ nghe thấy cô ấy hét lên với lũ quái vật, kiểu như "Dừng lại! Đừng làm thế!"... Có lẽ cô ấy đang cố ngăn chúng làm hại mọi người.</t>
         </is>
       </c>
     </row>
@@ -12441,7 +12441,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Có sự khác biệt đấy. Nhìn Dodget cọ trên bức này xem, nặng nề quá phải không? Có thể đoán Mingyan đang buồn bã khi vẽ nó. Còn bức này, Dodget cọ nhẹ nhàng, uyển chuyển. Chắc hẳn cô ấy vui vẻ khi vẽ đấy.</t>
+          <t>Có sự khác biệt đấy. Nhìn nét cọ trên bức này xem, nặng nề quá phải không? Có thể đoán Mingyan đang buồn bã khi vẽ nó. Còn bức này, nét cọ nhẹ nhàng, uyển chuyển. Chắc hẳn cô ấy vui vẻ khi vẽ đấy.</t>
         </is>
       </c>
     </row>
@@ -12506,7 +12506,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Cảm xúc của người họa sĩ trong quá trình sáng tạo thường ẩn mình trong từng Dodget cọ mà chính họ cũng không hay. Nó hiện diện trong từng đường Dodget, dù người nghệ sĩ có cố che giấu đi chăng nữa.</t>
+          <t>Cảm xúc của người họa sĩ trong quá trình sáng tạo thường ẩn mình trong từng nét cọ mà chính họ cũng không hay. Nó hiện diện trong từng đường nét, dù người nghệ sĩ có cố che giấu đi chăng nữa.</t>
         </is>
       </c>
     </row>
@@ -12571,7 +12571,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Hội Trao đổi Nghệ Thuật Shanyun là một tổ chức danh tiếng quản lý việc giao lưu thư pháp và hội họa tại Huanglong. Được lựa chọn trưng bày tác phẩm ở đây là một vinh dự lớn, mang lại uy tín vô cùng to lớn cho người nghệ sĩ.</t>
+          <t>Hội Trao Đổi Nghệ Thuật Shanyun là một tổ chức danh tiếng quản lý việc giao lưu thư pháp và hội họa tại Huanglong. Được lựa chọn trưng bày tác phẩm ở đây là một vinh dự lớn, mang lại uy tín vô cùng to lớn cho người nghệ sĩ.</t>
         </is>
       </c>
     </row>
@@ -13416,7 +13416,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Không way... Lũ quái vật đó xuất hiện giữa cánh đồng hoang lúc nửa đêm, chẳng có ai ở đó để trêu chọc cả. Mà chơi khăm làm gì nếu chẳng ai nhìn thấy?</t>
+          <t>Không đời nào... Lũ quái vật đó xuất hiện giữa cánh đồng hoang lúc nửa đêm, chẳng có ai ở đó để trêu chọc cả. Mà chơi khăm làm gì nếu chẳng ai nhìn thấy?</t>
         </is>
       </c>
     </row>
@@ -13481,7 +13481,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Ngươi nghĩ tụi ta sẽ để ngươi đi dễ dàng sau khi đã thấy hết cả kế hoạch à? Thôi được, có thể thương lượng, nhưng phải trả phí bảo hiểm tí chút.</t>
+          <t>Mày nghĩ tụi tao sẽ để mày đi dễ dàng sau khi đã thấy hết cả kế hoạch à? Thôi được, có thể thương lượng, nhưng phải trả phí bảo hiểm tí chút.</t>
         </is>
       </c>
     </row>
@@ -14261,7 +14261,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Very well. Chúng tôi sẽ xem xét lại cáo buộc đối với Mingyan, xác định mức độ liên quan của Shanyun Art Exchange trong vụ việc, và tiến hành điều tra toàn diện trong thời gian sớm nhất.</t>
+          <t>Được thôi. Chúng tôi sẽ xem xét lại cáo buộc đối với Mingyan, xác định mức độ liên quan của Shanyun Art Exchange trong vụ việc, và tiến hành điều tra toàn diện trong thời gian sớm nhất.</t>
         </is>
       </c>
     </row>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Mingyan lại mở bức tranh cuộn ra, nhìn ngắm từng chi tiết hồi lâu. Cô ấy như chìm đắm trong suy tư. Zhezhi và cậu lặng lẽ rời đi sau khi chứng kiến cảnh này.</t>
+          <t>Minh Nghiêm lại mở bức tranh cuộn ra, nhìn ngắm từng chi tiết hồi lâu. Cô ấy như chìm đắm trong suy tư. Triết Chi và cậu lặng lẽ rời đi sau khi chứng kiến cảnh này.</t>
         </is>
       </c>
     </row>
@@ -14911,7 +14911,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Huaijin tiết lộ rằng những con quái vật quanh khu mỏ gần đây đang hành động kỳ lạ, và gợi ý rằng chúng có thể liên quan đến vài bức tranh cuộn. Cô còn cảnh báo cậu rằng vụ này chắc chắn không chỉ có một người dính líu.</t>
+          <t>Hoài Cận tiết lộ rằng những con quái vật quanh khu mỏ gần đây đang hành động kỳ lạ, và gợi ý rằng chúng có thể liên quan đến vài bức tranh cuộn. Cô còn cảnh báo cậu rằng vụ này chắc chắn không chỉ có một người dính líu.</t>
         </is>
       </c>
     </row>
@@ -15366,7 +15366,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Trong số những bản phác thảo của Mingyan, Zhezhi nhận ra nhiều bản sao của bức *"Serenity Làng Xiehua"*, mỗi bức được vẽ theo cách khác nhau một cách tinh tế. Khi xem xét kỹ, Zhezhi để ý thấy vết màu loang trên quần áo cô và nhanh chóng nhận ra chất lượng sơn kém hơn bình thường.</t>
+          <t>Trong số những bản phác thảo của Mingyan, Zhezhi nhận ra nhiều bản sao của bức *"Bình Yên Làng Xiehua"*, mỗi bức được vẽ theo cách khác nhau một cách tinh tế. Khi xem xét kỹ, Zhezhi để ý thấy vết màu loang trên quần áo cô và nhanh chóng nhận ra chất lượng sơn kém hơn bình thường.</t>
         </is>
       </c>
     </row>
@@ -16081,7 +16081,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Trong kho của trại, cậu phát hiện vô số bản sao của những tác phẩm nghệ thuật nổi tiếng, chứng tỏ Mingyan đã bị ép phải làm giả tranh cho Sàn Giao Dịch Nghệ Thuật. Cậu lập tức chia sẻ thông tin này với Đội Tuần Tra. Trong khi đó, Zhezhi tìm thấy bức tranh gốc "Serenity Làng Xiehua" bị đánh cắp. Cô bắt đầu giải thích làm sao nhận ra nó giữa đống tranh giả, nhưng đột nhiên bị một bầy Tacet Discord chặn lại.</t>
+          <t>Trong kho của trại, cậu phát hiện vô số bản sao của những tác phẩm nghệ thuật nổi tiếng, chứng tỏ Mingyan đã bị ép phải làm giả tranh cho Sàn Giao Dịch Nghệ Thuật. Cậu lập tức chia sẻ thông tin này với Đội Tuần Tra. Trong khi đó, Zhezhi tìm thấy bức tranh gốc "Bình Yên Làng Xiehua" bị đánh cắp. Cô bắt đầu giải thích làm sao nhận ra nó giữa đống tranh giả, nhưng đột nhiên bị một bầy Tacet Discord chặn lại.</t>
         </is>
       </c>
     </row>
@@ -16146,7 +16146,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Yinfeng coi thường đam mê của người nghệ sĩ và cố bịt miệng cậu bằng tiền. Phẫn nộ nhưng kiên quyết, Chích Chỉ đứng vững, quyết tâm phơi bày mặt tối của Hội Nghệ Thuật Sơn Vân và giải cứu tất cả những nghệ sĩ bị ép buộc làm giả tác phẩm.</t>
+          <t>Âm Phong coi thường đam mê của người nghệ sĩ và cố bịt miệng cậu bằng tiền. Phẫn nộ nhưng kiên quyết, Chích Chỉ đứng vững, quyết tâm phơi bày mặt tối của Hội Nghệ Thuật Sơn Vân và giải cứu tất cả những nghệ sĩ bị ép buộc làm giả tác phẩm.</t>
         </is>
       </c>
     </row>
@@ -16536,7 +16536,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Nó giám sát &lt;te href=750035&gt;Etheric Sea&lt;/te&gt; trên toàn bộ Solaris. Do Tacetite ở đó mạnh hơn, sự nhiễu loạn cũng dữ dội hơn, nên cơ sở hạ tầng ở đó không nhiều.</t>
+          <t>Nó giám sát &lt;te href=750035&gt;Biển Ether&lt;/te&gt; trên toàn bộ Solaris. Do Tacetite ở đó mạnh hơn, sự nhiễu loạn cũng dữ dội hơn, nên cơ sở hạ tầng ở đó không nhiều.</t>
         </is>
       </c>
     </row>
@@ -16601,7 +16601,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Khi Mỏ Neo tại TD Observatory TD được khôi phục, một tần số chân chính trỗi dậy từ sâu thẳm, mang theo giọng nói vang lên trong tâm trí cậu. Nó tiết lộ rằng sự thức tỉnh của cậu tại Gorges of Spirits không hề ngẫu nhiên. Trước khi Yangyang tìm thấy cậu, đã có một bóng người bí ẩn theo dõi từng bước đi của cậu...</t>
+          <t>Khi Mỏ Neo tại Đài Quan Sát TD được khôi phục, một tần số chân chính trỗi dậy từ sâu thẳm, mang theo giọng nói vang lên trong tâm trí cậu. Nó tiết lộ rằng sự thức tỉnh của cậu tại Hẻm Núi Linh Hồn không hề ngẫu nhiên. Trước khi Yangyang tìm thấy cậu, đã có một bóng người bí ẩn theo dõi từng bước đi của cậu...</t>
         </is>
       </c>
     </row>
@@ -16731,7 +16731,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Khi Mỏ Neo tại Mắt Asteria được khôi phục, một tần số chân chính trỗi dậy từ sâu thẳm, mang theo giọng nói vang lên trong tâm trí cậu. Nó kể lại về Bờ Đen ngày xưa, nơi từng kết nối thế giới và đoàn kết mọi người chống lại Lament. Dù vậy, trận chiến vẫn còn lâu mới kết thúc...</t>
+          <t>Khi Mỏ Neo tại Mắt Asteria được khôi phục, một tần số chân chính trỗi dậy từ sâu thẳm, mang theo giọng nói vang lên trong tâm trí cậu. Nó kể lại về Bờ Đen ngày xưa, nơi từng kết nối thế giới và đoàn kết mọi người chống lại Lời Than Vãn. Dù vậy, trận chiến vẫn còn lâu mới kết thúc...</t>
         </is>
       </c>
     </row>
@@ -17326,7 +17326,7 @@
       <c r="M259" t="inlineStr">
         <is>
           <t>Trong lúc thu thập những mảnh ý kiến, cậu gặp một cô bé tên Ying, người chia sẻ với cậu tấm bản đồ kho báu dẫn tới Thanh Kiếm Dũng Khí. Tấm bản đồ này chứa đựng lời hứa giữa Ying và mẹ cô, với nguyện vọng sâu thẳm nhất của cô bé là được đoàn tụ với mẹ một lần nữa.
-Quyết tâm thực hiện ước nguyện của Ying và giúp cuộc phiêu lưu của Wooly Warrior có một cái kết viên mãn, cậu lên đường tìm kiếm ba bảo vật huyền thoại.</t>
+Quyết tâm thực hiện ước nguyện của Ying và giúp cuộc phiêu lưu của Chiến Binh Lông Xù có một cái kết viên mãn, cậu lên đường tìm kiếm ba bảo vật huyền thoại.</t>
         </is>
       </c>
     </row>
@@ -17592,7 +17592,7 @@
       <c r="M263" t="inlineStr">
         <is>
           <t>Với bao nỗ lực, cuối cùng cậu cũng lên đến đỉnh của cơ cấu và mở được rương—bên trong là Thanh Kiếm Dũng Khí và một lá thư bí ẩn.
-Lá thư tiết lộ rằng di vật tiếp theo, Shield Đức Tin, đang bị chôn sâu dưới lớp cát phía trước.</t>
+Lá thư tiết lộ rằng di vật tiếp theo, Khiên Đức Tin, đang bị chôn sâu dưới lớp cát phía trước.</t>
         </is>
       </c>
     </row>
@@ -17657,7 +17657,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Cuối cùng cũng đến rồi! Những nhà thám hiểm dũng cảm đã đặt chân đến điểm đến thứ hai, và giờ họ sẽ bắt đầu cuộc săn tìm chiếc Shield Đức Tin huyền thoại trên bãi cát này.</t>
+          <t>Cuối cùng cũng đến rồi! Những nhà thám hiểm dũng cảm đã đặt chân đến điểm đến thứ hai, và giờ họ sẽ bắt đầu cuộc săn tìm chiếc Khiên Đức Tin huyền thoại trên bãi cát này.</t>
         </is>
       </c>
     </row>
@@ -17723,8 +17723,8 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Sau khi tìm thấy Shield Đức Tin cùng một bức thư thứ hai, cậu biết được Wreath Hy Vọng đang được giấu trong Khu Garden.
-Ying sau đó tiết lộ rằng cô biết vị trí của Khu Garden, và hai người đồng ý cùng nhau đến đó.</t>
+          <t>Sau khi tìm thấy Khiên Đức Tin cùng một bức thư thứ hai, cậu biết được Vòng Hoa Hy Vọng đang được giấu trong Khu Vườn.
+Ying sau đó tiết lộ rằng cô biết vị trí của Khu Vườn, và hai người đồng ý cùng nhau đến đó.</t>
         </is>
       </c>
     </row>
@@ -17857,9 +17857,9 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Khi đến Garden, cậu thấy tất cả hoa Diên Vĩ đều đã héo úa.
+          <t>Khi đến Vườn, cậu thấy tất cả hoa Diên Vĩ đều đã héo úa.
 Ying nhận ra những bông hoa này vốn là món quà đặc biệt từ mẹ cô. Dù biết sẽ không bao giờ gặp lại mẹ, cô vẫn bày tỏ lòng biết ơn vì sự giúp đỡ của cậu.
-Tuy nhiên, Encore cảm nhận được nỗi buồn ẩn giấu sau vẻ bình thản của Ying và hứa với cô rằng sẽ trở lại Garden để chứng kiến hành trình của Đội Thám Hiểm Lông Xù.
+Tuy nhiên, Encore cảm nhận được nỗi buồn ẩn giấu sau vẻ bình thản của Ying và hứa với cô rằng sẽ trở lại Vườn để chứng kiến hành trình của Đội Thám Hiểm Lông Xù.
 Sau khi Ying rời đi, Encore tiết lộ với cậu nguồn gốc thật sự của câu chuyện Đội Thám Hiểm Lông Xù—đó là món quà quý giá từ chính mẹ của cô.</t>
         </is>
       </c>
@@ -17927,7 +17927,7 @@
       <c r="M268" t="inlineStr">
         <is>
           <t>Encore kể rằng câu chuyện này, được truyền lại từ mẹ cô, luôn là nguồn sức mạnh của cô. Với Encore, những câu chuyện không chỉ là lối thoát—mà còn là cách để tìm thấy dũng khí cho những cuộc phiêu lưu mới. Cô hy vọng có thể chia sẻ dũng khí ấy cho Ying.
-Quyết tâm thực hiện nguyện vọng của Ying và mang đến một kết thúc hoàn hảo cho câu chuyện của Encore, bạn và cô quyết định tạo nên một Wreath Hy Vọng. Để làm được điều này, các bạn tìm đến sự giúp đỡ của Verina.</t>
+Quyết tâm thực hiện nguyện vọng của Ying và mang đến một kết thúc hoàn hảo cho câu chuyện của Encore, bạn và cô quyết định tạo nên một Vòng Hoa Hy Vọng. Để làm được điều này, các bạn tìm đến sự giúp đỡ của Verina.</t>
         </is>
       </c>
     </row>
@@ -18187,7 +18187,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Rất tiếc là không. Sau khi đến được Biển Hoa huyền thoại, tất cả hoa đều đã tàn úa. Dù tìm kiếm khắp nơi, Wreath Hy Vọng vẫn biệt tăm.</t>
+          <t>Rất tiếc là không. Sau khi đến được Biển Hoa huyền thoại, tất cả hoa đều đã tàn úa. Dù tìm kiếm khắp nơi, Vòng Hoa Hy Vọng vẫn biệt tăm.</t>
         </is>
       </c>
     </row>
@@ -18252,7 +18252,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Giống như bây giờ vậy. Khi tình cảm của mọi người hòa quyện vào vòng hoa, nó dần biến thành một cánh cửa. Một cánh cửa dẫn đến nơi sâu thẳm nhất của Wooly Kingdom.</t>
+          <t>Giống như bây giờ vậy. Khi tình cảm của mọi người hòa quyện vào vòng hoa, nó dần biến thành một cánh cửa. Một cánh cửa dẫn đến nơi sâu thẳm nhất của Vương Quốc Lông Xù.</t>
         </is>
       </c>
     </row>
@@ -18319,9 +18319,9 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Vào giờ hẹn, cậu trở lại Khu Garden và lắng nghe Encore kể câu chuyện về Chiến binh Lông Xù – một cuộc phiêu lưu dành cho cả ba người.
-Khi câu chuyện kết thúc, cậu trao Wreath Hy Vọng cho Ying, chia sẻ những suy nghĩ và cảm xúc của mình với cô bé.
-Để hoàn thành Wreath Hy Vọng và giữ lời hứa với mẹ cô, cậu quyết định thực hiện chuyến đi cuối cùng đến Vương quốc Lông Xù, tìm kiếm những bông Diên Vĩ cuối cùng nở rộ.</t>
+          <t>Vào giờ hẹn, cậu trở lại Khu Vườn và lắng nghe Encore kể câu chuyện về Chiến binh Lông Xù – một cuộc phiêu lưu dành cho cả ba người.
+Khi câu chuyện kết thúc, cậu trao Vòng Hoa Hy Vọng cho Ying, chia sẻ những suy nghĩ và cảm xúc của mình với cô bé.
+Để hoàn thành Vòng Hoa Hy Vọng và giữ lời hứa với mẹ cô, cậu quyết định thực hiện chuyến đi cuối cùng đến Vương quốc Lông Xù, tìm kiếm những bông Diên Vĩ cuối cùng nở rộ.</t>
         </is>
       </c>
     </row>
@@ -18458,8 +18458,8 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Cậu ngồi xuống, chăm chú lắng nghe Encore kể câu chuyện về Wooly Warrior.
-Trong câu chuyện của cô, Wooly Warrior dấn thân vào cuộc hành trình đầy hiểm nguy để đoàn tụ với gia đình, tìm kiếm Cánh Cổng Điều Ước.
+          <t>Cậu ngồi xuống, chăm chú lắng nghe Encore kể câu chuyện về Chiến Binh Lông Xù.
+Trong câu chuyện của cô, Chiến Binh Lông Xù dấn thân vào cuộc hành trình đầy hiểm nguy để đoàn tụ với gia đình, tìm kiếm Cánh Cổng Điều Ước.
 "Nếu con tin vào câu chuyện này và muốn ước mơ của mình thành hiện thực, hãy nhắm mắt lại," Tiên Nữ Mây Lơ Lửng thì thầm.
 Nghe theo lời nàng, cậu nhắm mắt lại, sẵn sàng đắm chìm vào một cuộc phiêu lưu mới.</t>
         </is>
@@ -18527,7 +18527,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Cuối hành trình, ngươi gặp Tiên Mây, người tiết lộ rằng để đến được Cánh Cổng Ước Nguyện, ngươi phải thu thập ba bảo vật: Kiếm Dũng Khí, Shield Đức Tin và Wreath Hy Vọng.
+          <t>Cuối hành trình, ngươi gặp Tiên Mây, người tiết lộ rằng để đến được Cánh Cổng Ước Nguyện, ngươi phải thu thập ba bảo vật: Kiếm Dũng Khí, Khiên Đức Tin và Vòng Hoa Hy Vọng.
 Giờ thì, hãy bước qua cánh cổng và trở về thực tại.</t>
         </is>
       </c>
@@ -18594,8 +18594,8 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Đặt chân đến Wooly Kingdom, cậu và Encore hóa thân thành những nhà thám hiểm dũng cảm.
-Cánh cổng có thể thực hiện điều ước sâu thẳm nhất của các cậu đang ẩn mình trong lòng Wooly Kingdom.</t>
+          <t>Đặt chân đến Vương Quốc Lông Xù, cậu và Encore hóa thân thành những nhà thám hiểm dũng cảm.
+Cánh cổng có thể thực hiện điều ước sâu thẳm nhất của các cậu đang ẩn mình trong lòng Vương Quốc Lông Xù.</t>
         </is>
       </c>
     </row>
@@ -18661,7 +18661,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Sau bao thử thách gian nan, cuối cùng cậu cũng đứng trước Cổng Wish. Phía sau cánh cổng, đóa Hoa Hy Vọng đang chờ đợi.
+          <t>Sau bao thử thách gian nan, cuối cùng cậu cũng đứng trước Cổng Ước Nguyện. Phía sau cánh cổng, đóa Hoa Hy Vọng đang chờ đợi.
 Nếu đã sẵn sàng để ước nguyện thành hiện thực, hãy mở cánh cổng đó ra.</t>
         </is>
       </c>
@@ -19379,7 +19379,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Ngay cả Monica, quản trị viên trưởng của Black Shores, cũng chưa từng nghe đến cái tên Hoda. Ngay sau cuộc thảo luận của các cậu, một trận động đất lại rung chuyển Black Shores, vang vọng thảm họa ở Thành phố Cảng Guixu. Để bảo vệ Hệ thống Tethys, Monica chỉ thị cho cậu kiểm tra Thiết bị Modulation trong Nhà kính.</t>
+          <t>Ngay cả Monica, quản trị viên trưởng của Black Shores, cũng chưa từng nghe đến cái tên Hoda. Ngay sau cuộc thảo luận của các cậu, một trận động đất lại rung chuyển Black Shores, vang vọng thảm họa ở Thành phố Cảng Guixu. Để bảo vệ Hệ thống Tethys, Monica chỉ thị cho cậu kiểm tra Thiết bị Điều chế trong Nhà kính.</t>
         </is>
       </c>
     </row>
@@ -19509,7 +19509,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Anyway... để ta giới thiệu với cậu về KU-Money. Họ quản lý dòng tiền và theo dõi các thiết bị đầu cuối robot khắp khu vực. Họ chính là tay buôn khôn ngoan của Bờ Đen.</t>
+          <t>Dù sao... để ta giới thiệu với cậu về KU-Money. Họ quản lý dòng tiền và theo dõi các thiết bị đầu cuối robot khắp khu vực. Họ chính là tay buôn khôn ngoan của Bờ Đen.</t>
         </is>
       </c>
     </row>
@@ -19574,7 +19574,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Bạn giao dữ liệu cho con robot chuyên dụng tại Bờ Đen, nó nhanh chóng tải lên Tethys Hệ thống. Kẻ buôn bán tự xưng là KU-Money, có lẽ nhầm bạn là đồng nghiệp, đã thưởng cho bạn một khoản tiền lớn. Tuy nhiên, dù nắm rõ mọi ngóc ngách của Bờ Đen, con robot này lại chẳng biết gì về thân phận thật của Hoda.</t>
+          <t>Bạn giao dữ liệu cho con robot chuyên dụng tại Bờ Đen, nó nhanh chóng tải lên Hệ Thống Tethys. Kẻ buôn bán tự xưng là KU-Money, có lẽ nhầm bạn là đồng nghiệp, đã thưởng cho bạn một khoản tiền lớn. Tuy nhiên, dù nắm rõ mọi ngóc ngách của Bờ Đen, con robot này lại chẳng biết gì về thân phận thật của Hoda.</t>
         </is>
       </c>
     </row>
@@ -19834,7 +19834,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Tại Nhà Kính, cậu gặp hai con robot nhận ra cậu là Rover duy nhất của Solaris. Chúng nhắc đến Blake Blooms như thể cậu có mối liên hệ với họ, nhưng có vẻ như Tethys Hệ thống đang ngăn cản chúng tiết lộ sự thật về thân phận của cậu…</t>
+          <t>Tại Nhà Kính, cậu gặp hai con robot nhận ra cậu là Vận Mệnh Giả duy nhất của Solaris. Chúng nhắc đến Blake Blooms như thể cậu có mối liên hệ với họ, nhưng có vẻ như Hệ Thống Tethys đang ngăn cản chúng tiết lộ sự thật về thân phận của cậu…</t>
         </is>
       </c>
     </row>
@@ -20094,7 +20094,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>The Shorekeeper giải thích rằng trong thời gian cậu vắng mặt, cô và Tethys Hệ thống đã tiếp quản việc điều hành Bờ Đen. Cô xác nhận chính cô đã cứu cậu, Yangyang và Youhu tại Port City of Guixu. Để đối phó với những mối đe dọa từ Hoda và cuộc khủng hoảng đang cận kề ở cả Bờ Đen lẫn Port City of Guixu, The Shorekeeper đề nghị cậu mạo hiểm xuống lòng đất, nơi bầu trời đầy sao đang chờ đợi...</t>
+          <t>Người Gác Bờ giải thích rằng trong thời gian cậu vắng mặt, cô và Hệ Thống Tethys đã tiếp quản việc điều hành Bờ Đen. Cô xác nhận chính cô đã cứu cậu, Yangyang và Youhu tại Thành Phố Cảng Guixu. Để đối phó với những mối đe dọa từ Hoda và cuộc khủng hoảng đang cận kề ở cả Bờ Đen lẫn Thành Phố Cảng Guixu, Người Gác Bờ đề nghị cậu mạo hiểm xuống lòng đất, nơi bầu trời đầy sao đang chờ đợi...</t>
         </is>
       </c>
     </row>
@@ -20159,7 +20159,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Rồi cậu cần đến Trung Tâm Data, nơi lưu trữ các Ma Trận Sao... ý tớ là bộ sưu tập sao ấy. Đáng tiếc là nó đã ngừng hoạt động từ lâu rồi.</t>
+          <t>Rồi cậu cần đến Trung Tâm Dữ Liệu, nơi lưu trữ các Ma Trận Sao... ý tớ là bộ sưu tập sao ấy. Đáng tiếc là nó đã ngừng hoạt động từ lâu rồi.</t>
         </is>
       </c>
     </row>
@@ -20224,7 +20224,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Cuối cùng, cậu và Người Gác Bến cũng đến được Error Cell nơi Necrostar rơi xuống. Nhưng nhiều người bị thương ở đây đã bị dữ liệu nhiễm độc ảnh hưởng nghiêm trọng, không thể cứu chữa.</t>
+          <t>Cuối cùng, cậu và Người Gác Bến cũng đến được Tế Bào Lỗi nơi Necrostar rơi xuống. Nhưng nhiều người bị thương ở đây đã bị dữ liệu nhiễm độc ảnh hưởng nghiêm trọng, không thể cứu chữa.</t>
         </is>
       </c>
     </row>
@@ -20289,7 +20289,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>The Shorekeeper có thể cảm nhận được những cảm xúc ẩn sâu bên dưới sự dối trá, thương hại và các hành vi khác, nhưng cô khó lòng hiểu thấu chúng. Cô tiết lộ rằng dữ liệu cậu thu thập được liên quan đến Nỗi Bi Thương từ Port City of Guixu, và Tethys Hệ thống đang sử dụng chính Nỗi Bi Thương ấy để chống lại nó...</t>
+          <t>Người Gác Bờ có thể cảm nhận được những cảm xúc ẩn sâu bên dưới sự dối trá, thương hại và các hành vi khác, nhưng cô khó lòng hiểu thấu chúng. Cô tiết lộ rằng dữ liệu cậu thu thập được liên quan đến Nỗi Bi Thương từ Thành Phố Cảng Guixu, và Hệ Thống Tethys đang sử dụng chính Nỗi Bi Thương ấy để chống lại nó...</t>
         </is>
       </c>
     </row>
@@ -20484,7 +20484,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Bị cuốn vào dòng chảy Sonoro dâng trào của cô ấy, ngươi bị kéo vào những thảm họa mà Người Gác Bờ đã "trải qua" khi phân tích Lament. Hình hài của cô, được tạo nên bởi Sonoro Sphere, bị ràng buộc bởi những tính toán của hệ thống Tethys. Duy nhất một khát khao thôi thúc cô: bảo vệ ngươi và Black Shores, nhưng sâu trong tim vẫn ẩn chứa một sự thật bí mật...</t>
+          <t>Bị cuốn vào dòng chảy Sonoro dâng trào của cô ấy, ngươi bị kéo vào những thảm họa mà Người Gác Bờ đã "trải qua" khi phân tích Lament. Hình hài của cô, được tạo nên bởi Sonoro Sphere, bị ràng buộc bởi những tính toán của hệ thống Tethys. Duy nhất một khát khao thôi thúc cô: bảo vệ ngươi và Bờ Biển Đen, nhưng sâu trong tim vẫn ẩn chứa một sự thật bí mật...</t>
         </is>
       </c>
     </row>
@@ -20809,7 +20809,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>The Shorekeeper và cậu quay trở lại thực tại, hạ cánh xuống chính bãi biển nơi cậu lần đầu đặt chân đến Bờ Đen. Cô giải thích về sự dối trá liên quan đến Ma Trận Sao và bày tỏ lòng biết ơn.</t>
+          <t>Người Gác Bờ và cậu quay trở lại thực tại, hạ cánh xuống chính bãi biển nơi cậu lần đầu đặt chân đến Bờ Đen. Cô giải thích về sự dối trá liên quan đến Ma Trận Sao và bày tỏ lòng biết ơn.</t>
         </is>
       </c>
     </row>
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>The Shorekeeper cảnh báo cậu về những bất thường của Abby. Nhờ sự can thiệp của cậu, Hệ thống Tethys đã trở lại trạng thái chính đáng, vận hành với những tần số hòa bình và hài hòa.</t>
+          <t>Người Gác Bờ cảnh báo cậu về những bất thường của Abby. Nhờ sự can thiệp của cậu, Hệ thống Tethys đã trở lại trạng thái chính đáng, vận hành với những tần số hòa bình và hài hòa.</t>
         </is>
       </c>
     </row>
@@ -21004,7 +21004,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Youhu tiết lộ manh mối mà Hoda nhắc đến chính là một cổ vật từ Núi Firmament, do cô và Master Chenpi phát hiện. Giờ đây, nó dường như có liên hệ với Black Shores. Tần số gắn liền với Hoda đang ẩn giấu trong cổ vật này, và có vẻ như nó liên quan đến cái chết của những Người Gìn Giữ Hoa. Việc báo cáo chuyện này cho Niya và Black Shores giờ đây là vấn đề cấp bách.</t>
+          <t>Youhu tiết lộ manh mối mà Hoda nhắc đến chính là một cổ vật từ Núi Firmament, do cô và Sư phụ Chenpi phát hiện. Giờ đây, nó dường như có liên hệ với Bờ Biển Đen. Tần số gắn liền với Hoda đang ẩn giấu trong cổ vật này, và có vẻ như nó liên quan đến cái chết của những Người Gìn Giữ Hoa. Việc báo cáo chuyện này cho Niya và Bờ Biển Đen giờ đây là vấn đề cấp bách.</t>
         </is>
       </c>
     </row>
@@ -21199,7 +21199,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Cuối cùng, cậu và Người Gác Bến cũng đến được Port City of Guixu mô phỏng. Thành phố tráng lệ này đang đứng bên bờ vực hủy diệt với hai Lament khổng lồ án ngữ, niêm phong số phận của nó. Dù lịch sử không thể thay đổi, cậu chỉ có thể sống lại những khoảnh khắc kinh hoàng khi thành phố sụp đổ và nỗi tuyệt vọng bao trùm.</t>
+          <t>Cuối cùng, cậu và Người Gác Bến cũng đến được Thành Phố Cảng Guixu mô phỏng. Thành phố tráng lệ này đang đứng bên bờ vực hủy diệt với hai Lament khổng lồ án ngữ, niêm phong số phận của nó. Dù lịch sử không thể thay đổi, cậu chỉ có thể sống lại những khoảnh khắc kinh hoàng khi thành phố sụp đổ và nỗi tuyệt vọng bao trùm.</t>
         </is>
       </c>
     </row>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Cậu đã sa vào mạng lưới dữ liệu rối rắm của Tethys Hệ thống. Để ngăn cản cậu giải cứu Shorekeeper – kẻ sắp trở thành lõi của nó – Tethys phơi bày ba tương lai có thể xảy ra nếu thiếu hắn: kỷ băng hà, thảm họa diệt vong, và sự tái thiết hoàn toàn nền văn minh. Từ một công cụ quan sát các nền văn minh, hệ thống lạnh lùng và tính toán này giờ đây công khai chống lại cậu. Trận chiến cuối cùng đã cận kề – ai sẽ là kẻ chiến thắng, cậu hay Tethys?</t>
+          <t>Cậu đã sa vào mạng lưới dữ liệu rối rắm của Hệ Thống Tethys. Để ngăn cản cậu giải cứu Shorekeeper – kẻ sắp trở thành lõi của nó – Tethys phơi bày ba tương lai có thể xảy ra nếu thiếu hắn: kỷ băng hà, thảm họa diệt vong, và sự tái thiết hoàn toàn nền văn minh. Từ một công cụ quan sát các nền văn minh, hệ thống lạnh lùng và tính toán này giờ đây công khai chống lại cậu. Trận chiến cuối cùng đã cận kề – ai sẽ là kẻ chiến thắng, cậu hay Tethys?</t>
         </is>
       </c>
     </row>
@@ -21851,7 +21851,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Yep! Không thể trông đợi mọi thiết kế sản phẩm đều thành công ngay từ đầu được. Chúng ta cần nghĩ ra thêm thật nhiều ý tưởng hay ho hơn nữa để thu hút sự chú ý của người Ragunnesi.</t>
+          <t>Ừa! Không thể trông đợi mọi thiết kế sản phẩm đều thành công ngay từ đầu được. Chúng ta cần nghĩ ra thêm thật nhiều ý tưởng hay ho hơn nữa để thu hút sự chú ý của người Ragunnesi.</t>
         </is>
       </c>
     </row>
@@ -22176,7 +22176,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Camellya rất thích trò chơi và trao cho cậu chiếc vòng tay như đã hứa. Nhận ra sự trợ giúp của cô là vô cùng quan trọng để giải quyết cuộc khủng hoảng hiện tại, cậu đề nghị cô ở lại. Camellya thấy sự quyết đoán của cậu thật thú vị và đồng ý giúp đỡ. Trong cuộc trò chuyện về bản thân và những ký ức đã mất, Camellya khẳng định bản năng mới là thứ định nghĩa con người cô. Để thu thập thêm vật phẩm của Lady Flora, hai người quyết định tách ra.</t>
+          <t>Camellya rất thích trò chơi và trao cho cậu chiếc vòng tay như đã hứa. Nhận ra sự trợ giúp của cô là vô cùng quan trọng để giải quyết cuộc khủng hoảng hiện tại, cậu đề nghị cô ở lại. Camellya thấy sự quyết đoán của cậu thật thú vị và đồng ý giúp đỡ. Trong cuộc trò chuyện về bản thân và những ký ức đã mất, Camellya khẳng định bản năng mới là thứ định nghĩa con người cô. Để thu thập thêm vật phẩm của Quý bà Flora, hai người quyết định tách ra.</t>
         </is>
       </c>
     </row>
@@ -22243,7 +22243,7 @@
       <c r="M334" t="inlineStr">
         <is>
           <t>Camellya có dấu hiệu Quá Tải sau trận chiến, nhưng cô không hề bận tâm. Cô đã quen với nỗi đau và giải thích rằng tận hưởng từng khoảnh khắc hiện tại là cách cô đối phó.
-Từ tần số của Blake Bloom, bạn phát hiện ra rằng Lady Flora đã biến mất cùng thời điểm với thủ lĩnh Black Shores. Sau khi thu thập đủ vật phẩm, bạn tiến đến Đại Sảnh Điều Chỉnh.</t>
+Từ tần số của Blake Bloom, bạn phát hiện ra rằng Quý bà Flora đã biến mất cùng thời điểm với thủ lĩnh Bờ Biển Đen. Sau khi thu thập đủ vật phẩm, bạn tiến đến Đại Sảnh Điều Chỉnh.</t>
         </is>
       </c>
     </row>
@@ -22438,7 +22438,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>"Lady Flora" rất nguy hiểm—trí tuệ và khả năng ngôn ngữ của bà bị tổn thương, khiến bà dễ có những hành động liều lĩnh. Bà là mối đe dọa đối với các cơ sở nội bộ của Black Shores.</t>
+          <t>"Quý bà Flora" rất nguy hiểm—trí tuệ và khả năng ngôn ngữ của bà bị tổn thương, khiến bà dễ có những hành động liều lĩnh. Bà là mối đe dọa đối với các cơ sở nội bộ của Bờ Biển Đen.</t>
         </is>
       </c>
     </row>
@@ -22503,7 +22503,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>(Bản ghi trước có nhắc đến &lt;color=Highlight&gt;một vài người sống sót sau Sự Cố Discord, nhưng ở Làng Petalfall này, tất cả đều đã chết, ngoại trừ Camellya.&lt;/color&gt;)</t>
+          <t>(Bản ghi trước có nhắc đến &lt;color=Highlight&gt;một vài người sống sót sau Sự Cố Tacet Discord, nhưng ở Làng Petalfall này, tất cả đều đã chết, ngoại trừ Camellya.&lt;/color&gt;)</t>
         </is>
       </c>
     </row>
@@ -22830,7 +22830,7 @@
       <c r="M343" t="inlineStr">
         <is>
           <t>Khi lại một lần băng qua Cánh Cổng Sao, cậu gặp một phiên bản khác của Quý Cô Flora tại Bãi Đen. Khác với Quý Cô Flora trước đây, lần này bà trông khỏe mạnh và có chút ngại ngùng, nhưng lòng ngưỡng mộ dành cho cậu vẫn không hề thay đổi. Bà nói rằng gặp cậu khiến bà cảm thấy quen thuộc.
-Nhờ sự xuất hiện kịp thời của cậu, Làng Petalfall đã thoát khỏi thảm họa tại mốc thời gian này, dù sự thật không phải vậy. Like lần trước, Quý Cô Flora mỉm cười và tặng cậu một bông hoa.</t>
+Nhờ sự xuất hiện kịp thời của cậu, Làng Petalfall đã thoát khỏi thảm họa tại mốc thời gian này, dù sự thật không phải vậy. Giống như lần trước, Quý Cô Flora mỉm cười và tặng cậu một bông hoa.</t>
         </is>
       </c>
     </row>
@@ -22962,7 +22962,7 @@
       <c r="M345" t="inlineStr">
         <is>
           <t>Sau khi đi qua Cổng Sao lần thứ ba, ngươi cuối cùng cũng đến được điểm giao thời gian chính xác.
-Lady Flora mà ngươi gặp có ngoại hình giống Camellya ở thế giới thực và cũng như những người khác, bà không giấu giếm tình cảm dành cho ngươi.</t>
+Quý bà Flora mà ngươi gặp có ngoại hình giống Camellya ở thế giới thực và cũng như những người khác, bà không giấu giếm tình cảm dành cho ngươi.</t>
         </is>
       </c>
     </row>
@@ -23159,7 +23159,7 @@
       <c r="M348" t="inlineStr">
         <is>
           <t>Trong lúc lặn, có điều gì đó bất ổn xảy ra. Bạn mất liên lạc với Camellya và Đại Sảnh Điều Chỉnh.
-Bên kia Cổng Sao, bạn thấy mình trong một hang động kỳ lạ. Tại đó, ảo ảnh của Lady Flora, trông giống hệt Camellya, hiện ra trước mắt bạn.</t>
+Bên kia Cổng Sao, bạn thấy mình trong một hang động kỳ lạ. Tại đó, ảo ảnh của Quý bà Flora, trông giống hệt Camellya, hiện ra trước mắt bạn.</t>
         </is>
       </c>
     </row>
@@ -23225,7 +23225,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Mất liên lạc với cậu, Camellya vượt qua Stargate và lạc vào hang động của quá khứ. Like cậu, cô đã trải qua nhiều thế giới mô phỏng và chứng kiến những khả năng khác nhau, nhưng con đường của cô luôn giao với cậu.
+          <t>Mất liên lạc với cậu, Camellya vượt qua Stargate và lạc vào hang động của quá khứ. Giống như cậu, cô đã trải qua nhiều thế giới mô phỏng và chứng kiến những khả năng khác nhau, nhưng con đường của cô luôn giao với cậu.
 Bị thu hút bởi ảo ảnh Lady Flora trước mặt, Camellya quyết định đi theo.</t>
         </is>
       </c>
@@ -23291,7 +23291,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Lady Flora giải thích rằng những nhiệm vụ trong quá khứ áp đặt lên người mà nàng khao khát đã khiến người ấy quyết định rời Bờ Đen. Camellya lắng nghe bản thân quá khứ của mình, ngạc nhiên trước chiều sâu cảm xúc ấy. Qua lời Lady Flora, Camellya nhận ra cậu chính là thủ lĩnh của Bờ Đen.</t>
+          <t>Quý bà Flora giải thích rằng những nhiệm vụ trong quá khứ áp đặt lên người mà nàng khao khát đã khiến người ấy quyết định rời Bờ Đen. Camellya lắng nghe bản thân quá khứ của mình, ngạc nhiên trước chiều sâu cảm xúc ấy. Qua lời Quý bà Flora, Camellya nhận ra cậu chính là thủ lĩnh của Bờ Đen.</t>
         </is>
       </c>
     </row>
@@ -23356,7 +23356,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Tình trạng của Lady Flora ngày càng tồi tệ kể từ khi nàng mất đi Anchor. Khi những ký ức trước khi đến Làng Petalfall trỗi dậy, triệu chứng Overclocking của nàng càng thêm trầm trọng. Camellya vật lộn để hiểu thế nào là quan tâm đến người khác.</t>
+          <t>Tình trạng của Quý bà Flora ngày càng tồi tệ kể từ khi nàng mất đi Anchor. Khi những ký ức trước khi đến Làng Petalfall trỗi dậy, triệu chứng Overclocking của nàng càng thêm trầm trọng. Camellya vật lộn để hiểu thế nào là quan tâm đến người khác.</t>
         </is>
       </c>
     </row>
@@ -23421,7 +23421,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Lady Flora từ chối điều trị vì sợ sẽ chẳng còn gì. Nếu mất đi sức mạnh, nàng sẽ mãi cảm thấy thấp kém trước người mình trân trọng, điều mà nàng không thể chấp nhận. Bầu không khí nặng nề khiến triệu chứng Overclocking của Camellya cũng bùng phát.</t>
+          <t>Quý bà Flora từ chối điều trị vì sợ sẽ chẳng còn gì. Nếu mất đi sức mạnh, nàng sẽ mãi cảm thấy thấp kém trước người mình trân trọng, điều mà nàng không thể chấp nhận. Bầu không khí nặng nề khiến triệu chứng Overclocking của Camellya cũng bùng phát.</t>
         </is>
       </c>
     </row>
@@ -24012,7 +24012,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Sự bùng phát của Echo đã giải phóng tác phẩm mới nhất của Ovathrax: Dreamless, một thực thể chưa hoàn thiện. Khi thành phố Jinzhou bị bao vây, cậu đã tham chiến, cuối cùng đánh bại Dreamless và hấp thụ nó bằng chính đôi tay mình.</t>
+          <t>Sự bùng phát của Tổ Tacet đã giải phóng tác phẩm mới nhất của Ovathrax: Dreamless, một thực thể chưa hoàn thiện. Khi thành phố Jinzhou bị bao vây, cậu đã tham chiến, cuối cùng đánh bại Dreamless và hấp thụ nó bằng chính đôi tay mình.</t>
         </is>
       </c>
     </row>
@@ -24207,7 +24207,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Xinyi, thị trưởng của Hồng Chấn, thông báo với cậu rằng Jinhsi vừa mới rời đi lên đỉnh núi Thiên Cương để tìm kiếm Sentinel. Do sự méo mó thời gian, những gì cậu trải qua trong mấy ngày chỉ là khoảnh khắc ngắn ngủi bên trong ngọn núi.</t>
+          <t>Tân Nghi, thị trưởng của Hồng Chấn, thông báo với cậu rằng Jinhsi vừa mới rời đi lên đỉnh núi Thiên Cương để tìm kiếm Sentinel. Do sự méo mó thời gian, những gì cậu trải qua trong mấy ngày chỉ là khoảnh khắc ngắn ngủi bên trong ngọn núi.</t>
         </is>
       </c>
     </row>
@@ -24402,7 +24402,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Theo sự dẫn dắt của Jué, cậu bước vào con đường mới, truy tìm câu trả lời cho bí ẩn về nguồn gốc của mình. Điểm đến tiếp theo là căn cứ của một tổ chức bí ẩn mang tên Black Shores.</t>
+          <t>Theo sự dẫn dắt của Jué, cậu bước vào con đường mới, truy tìm câu trả lời cho bí ẩn về nguồn gốc của mình. Điểm đến tiếp theo là căn cứ của một tổ chức bí ẩn mang tên Bờ Biển Đen.</t>
         </is>
       </c>
     </row>
@@ -24467,7 +24467,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Bạn cùng Yangyang đối mặt với cuộc khủng hoảng ở Port City of Guixu. Ngay sau đó, Người Gác Bờ dẫn bạn đến Black Shores, một nơi bí ẩn. Hệ thống Tethys ở đây đã gặp sự cố nghiêm trọng, giải phóng ô nhiễm dữ liệu ăn mòn mọi thứ nó chạm vào.</t>
+          <t>Bạn cùng Yangyang đối mặt với cuộc khủng hoảng ở Thành Phố Cảng Guixu. Ngay sau đó, Người Gác Bờ dẫn bạn đến Bờ Biển Đen, một nơi bí ẩn. Hệ thống Tethys ở đây đã gặp sự cố nghiêm trọng, giải phóng ô nhiễm dữ liệu ăn mòn mọi thứ nó chạm vào.</t>
         </is>
       </c>
     </row>
@@ -24532,7 +24532,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>The Shorekeeper tiết lộ rằng cậu từng là thủ lĩnh và người sáng lập Black Shores, một tổ chức cổ xưa trải qua nhiều thời đại, còn cô ấy là trợ thủ trung thành của cậu.</t>
+          <t>Người Gác Bờ tiết lộ rằng cậu từng là thủ lĩnh và người sáng lập Black Shores, một tổ chức cổ xưa trải qua nhiều thời đại, còn cô ấy là trợ thủ trung thành của cậu.</t>
         </is>
       </c>
     </row>
@@ -24662,7 +24662,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Để giải quyết hỗn loạn do Hệ thống Tethys gây ra, cậu và Người Gác Bờ đã bước vào mô phỏng mà nó tạo ra, sống lại giờ phút cuối cùng trước khi Lament ập xuống Thành phố Guixu.</t>
+          <t>Để giải quyết hỗn loạn do Hệ thống Tethys gây ra, cậu và Người Gác Bờ đã bước vào mô phỏng mà nó tạo ra, sống lại giờ phút cuối cùng trước khi Lời Than Vãn ập xuống Thành phố Guixu.</t>
         </is>
       </c>
     </row>
@@ -24922,7 +24922,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Hỡi Rover được thủy triều dẫn lối, ngươi đã xua tan bóng tối chiến tranh ở Jinzhou và vượt qua ranh giới thời gian trên đỉnh Núi Firmament. Khi đứng trên bờ biển cô tịch, ngươi có nghe thấy lời phúc âm vang trên gió bão, vọng qua biển động không? Ngươi có thoáng thấy vẻ huy hoàng vô song ẩn giấu trong vùng đất huyền thoại của những Echo không? Giờ đây, hãy tôi rèn lòng dũng cảm, dấn thân vào chốn vô định, đương đầu với bão tố và mở đường đến Rinascita.</t>
+          <t>Hỡi Vận Mệnh Giả được thủy triều dẫn lối, ngươi đã xua tan bóng tối chiến tranh ở Jinzhou và vượt qua ranh giới thời gian trên đỉnh Núi Firmament. Khi đứng trên bờ biển cô tịch, ngươi có nghe thấy lời phúc âm vang trên gió bão, vọng qua biển động không? Ngươi có thoáng thấy vẻ huy hoàng vô song ẩn giấu trong vùng đất huyền thoại của những Tiếng Vọng không? Giờ đây, hãy tôi rèn lòng dũng cảm, dấn thân vào chốn vô định, đương đầu với bão tố và mở đường đến Rinascita.</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Bóng tối dần tan khi ánh sáng yếu ớt chiếu lên tấm thảm đỏ thẫm. Ngươi thấy mình đang đứng trong một hành lang treo đầy áp phích. Chắc hẳn đây là nơi tổ chức Liên hoan Film Somnoire.</t>
+          <t>Bóng tối dần tan khi ánh sáng yếu ớt chiếu lên tấm thảm đỏ thẫm. Ngươi thấy mình đang đứng trong một hành lang treo đầy áp phích. Chắc hẳn đây là nơi tổ chức Liên hoan Phim Somnoire.</t>
         </is>
       </c>
     </row>
@@ -25182,7 +25182,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>"À, hai vị đây... Tôi đã hiểu rồi. Chào mừng đến với Liên hoan Film Somnoire. Tôi là người dẫn chương trình, đồng thời là nhà sản xuất của những bộ phim các vị sắp được xem. Xin phép được hỏi, tôi nên gọi {Male=ngài;Female=bà} như thế nào ạ?"</t>
+          <t>"À, hai vị đây... Tôi đã hiểu rồi. Chào mừng đến với Liên hoan Phim Somnoire. Tôi là người dẫn chương trình, đồng thời là nhà sản xuất của những bộ phim các vị sắp được xem. Xin phép được hỏi, tôi nên gọi {Male=sir;Female=madam} như thế nào ạ?"</t>
         </is>
       </c>
     </row>
@@ -25312,7 +25312,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>"Rất vinh hạnh. Gần đây, hoạt động ở Somnoire gia tăng, chúng tôi đón nhận nhiều du khách từ các tầng khác. Tôi rất vinh dự được giới thiệu với anh về Liên hoan Film Solaris, một sự kiện tôn vinh những bộ phim sinh ra từ những giấc mơ và tần số của chính Somnoire. Nhiệm vụ của đoàn chúng tôi là đảm bảo mỗi bộ phim đều mang một bản sắc riêng, tạo nên trải nghiệm khó quên cho mỗi khán giả."</t>
+          <t>"Rất vinh hạnh. Gần đây, hoạt động ở Somnoire gia tăng, chúng tôi đón nhận nhiều du khách từ các tầng khác. Tôi rất vinh dự được giới thiệu với anh về Liên hoan Phim Solaris, một sự kiện tôn vinh những bộ phim sinh ra từ những giấc mơ và tần số của chính Somnoire. Nhiệm vụ của đoàn chúng tôi là đảm bảo mỗi bộ phim đều mang một bản sắc riêng, tạo nên trải nghiệm khó quên cho mỗi khán giả."</t>
         </is>
       </c>
     </row>
@@ -25702,7 +25702,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>"Bạn never know. Dù sao, các nhà làm phim luôn có bí mật của riêng họ... Nhưng thật ra, khán giả cũng chẳng quan tâm đâu. Dù ngươi tìm thấy gì, đó cũng là của riêng ngươi."</t>
+          <t>"Ai mà biết được. Dù sao, các nhà làm phim luôn có bí mật của riêng họ... Nhưng thật ra, khán giả cũng chẳng quan tâm đâu. Dù ngươi tìm thấy gì, đó cũng là của riêng ngươi."</t>
         </is>
       </c>
     </row>
@@ -26157,7 +26157,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>"Mọi thứ trong bộ phim đó đều như thật quá. Ngọn núi, tuyết rơi... Phù, giờ nghĩ lại vẫn còn nổi da gà. À, còn đồ ăn ở quán trọ đó nữa! Ngon tuyệt cú mèo! Ta nên bắt đầu viết nhật ký ẩm thực để ghi lại tất cả những món ngon đã nếm thử."</t>
+          <t>"Mọi thứ trong bộ phim đó đều như thật quá. Ngọn núi, tuyết rơi... Phù, giờ nghĩ lại vẫn còn nổi da gà. À, còn đồ ăn ở quán trọ đó nữa! Ngon tuyệt cú mèo! Tao nên bắt đầu viết nhật ký ẩm thực để ghi lại tất cả những món ngon đã nếm thử."</t>
         </is>
       </c>
     </row>
@@ -26287,7 +26287,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>"Bọn ta làm trong ngành này bao lâu rồi nhỉ? Đừng hiểu lầm, ta vẫn đam mê điện ảnh, chỉ tiếc là thực tại không phải lúc nào cũng tươi đẹp như trên phim thôi."</t>
+          <t>"Bọn tao làm trong ngành này bao lâu rồi nhỉ? Đừng hiểu lầm, tao vẫn đam mê điện ảnh, chỉ tiếc là thực tại không phải lúc nào cũng tươi đẹp như trên phim thôi."</t>
         </is>
       </c>
     </row>
@@ -26612,7 +26612,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>"Này, cậu nghĩ cảnh đó mà quay dài thêm chút, rồi thêm hiệu ứng rung nhẹ thì sao? Rồi mình có thể bỏ bớt vài khung hình và tăng sáng hậu kỳ. Ta nghĩ thế là ngon. Ta sẽ nói với chị phụ ánh sáng xem có thể kiếm mấy viên khói để thể hiện lúc nhân vật chính bước vào thế giới nội tâm không. Cậu thấy sao, anh bạn?"</t>
+          <t>"Này, cậu nghĩ cảnh đó mà quay dài thêm chút, rồi thêm hiệu ứng rung nhẹ thì sao? Rồi mình có thể bỏ bớt vài khung hình và tăng sáng hậu kỳ. Tao nghĩ thế là ngon. Tao sẽ nói với chị phụ ánh sáng xem có thể kiếm mấy viên khói để thể hiện lúc nhân vật chính bước vào thế giới nội tâm không. Cậu thấy sao, anh bạn?"</t>
         </is>
       </c>
     </row>
@@ -26677,7 +26677,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>"Hello! Tôi là nhân viên của lễ hội và cũng là quay phim cho đoàn làm phim của chúng ta. Đây là biên tập viên của chúng tôi. Chào mừng cậu! Hy vọng cậu đã thích những bộ phim nhé."</t>
+          <t>"Xin chào! Tôi là nhân viên của lễ hội và cũng là quay phim cho đoàn làm phim của chúng ta. Đây là biên tập viên của chúng tôi. Chào mừng cậu! Hy vọng cậu đã thích những bộ phim nhé."</t>
         </is>
       </c>
     </row>
@@ -27132,7 +27132,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Ta sẽ không đấu với hắn nữa. Không phải để làm trò giải trí. Không phải để diễn lại vở hài kịch tàn nhẫn cho những ánh mắt vô tâm. Vậy nên, hãy thay ta đối mặt với hắn. Hãy cho hắn cuộc đấu cuối xứng đáng.</t>
+          <t>Tao sẽ không đấu với hắn nữa. Không phải để làm trò giải trí. Không phải để diễn lại vở hài kịch tàn nhẫn cho những ánh mắt vô tâm. Vậy nên, hãy thay tao đối mặt với hắn. Hãy cho hắn cuộc đấu cuối xứng đáng.</t>
         </is>
       </c>
     </row>
@@ -27392,7 +27392,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>{Male=Ngài;Female=Quý cô} {PlayerName}, đòn đánh đó thật tuyệt diệu! Chỉ một nhát, ngươi đã hạ gục ta! Ta gần như cảm nhận được lòng trắc ẩn vang lên trong lưỡi kiếm của ngươi…</t>
+          <t>{Male=Mr.;Female=Ms.} {PlayerName}, đòn đánh đó thật tuyệt diệu! Chỉ một nhát, ngươi đã hạ gục ta! Ta gần như cảm nhận được lòng trắc ẩn vang lên trong lưỡi kiếm của ngươi…</t>
         </is>
       </c>
     </row>
@@ -27457,7 +27457,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Nhưng khi ta đến, cô ấy đã biến mất. Một nhân viên với đôi mắt thâm quầng thảm hại bảo ta cô ấy đã đi đến quần đảo Riccioli. Thế là ta gom góp hết tiền bạc, mua vé đi ngay.</t>
+          <t>Nhưng khi tao đến, cô ấy đã biến mất. Một nhân viên với đôi mắt thâm quầng thảm hại bảo tao cô ấy đã đi đến quần đảo Riccioli. Thế là tao gom góp hết tiền bạc, mua vé đi ngay.</t>
         </is>
       </c>
     </row>
@@ -27652,7 +27652,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Dòng chữ trên khiên ghi: Tài sản của Nolon. Dùng khi cần—Fictro không kèm theo! Nếu ngươi còn vẽ bậy lên khiên của ta, ta sẽ cho ngươi nếm trải Sóng Hắc Ám!</t>
+          <t>Dòng chữ trên khiên ghi: Tài sản của Nolon. Dùng khi cần—Fictro không kèm theo! Nếu mày còn vẽ bậy lên khiên của tao, tao sẽ cho mày nếm trải Sóng Hắc Ám!</t>
         </is>
       </c>
     </row>
@@ -27719,7 +27719,7 @@
       <c r="M418" t="inlineStr">
         <is>
           <t>Con dao bên trái có bốn mươi vạch khắc, có lẽ tượng trưng cho số sinh vật Dark Tide mà chủ nhân của nó đã săn được.
-Con dao bên phải chỉ có chín vạch với dòng chữ bên dưới: Số lần ta đá đít Fictro.</t>
+Con dao bên phải chỉ có chín vạch với dòng chữ bên dưới: Số lần tao đá đít Fictro.</t>
         </is>
       </c>
     </row>
@@ -27855,7 +27855,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Bond Băng Giá với môn trượt tuyết đổ đèo tại Núi Firmament; Sức Mạnh Nổi Lên với môn chèo thuyền vượt thác tại Quần đảo Riccioli—và còn nhiều nữa. Tất cả tám mối liên kết ấy đều nằm rải rác khắp Solaris.</t>
+          <t>Mối Liên Kết Băng Giá với môn trượt tuyết đổ đèo tại Núi Firmament; Sức Mạnh Nổi Lên với môn chèo thuyền vượt thác tại Quần đảo Riccioli—và còn nhiều nữa. Tất cả tám mối liên kết ấy đều nằm rải rác khắp Solaris.</t>
         </is>
       </c>
     </row>
@@ -28966,7 +28966,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Yes. Bằng cách sử dụng Sonance Casket, bức tranh biến hình có thể ổn định những Echo vô chủ tại đây bằng Trường Thanh Âm của nó, ngăn chúng tan biến hay trở nên thù địch.</t>
+          <t>Đúng vậy. Bằng cách sử dụng Hòm Thanh Âm, bức tranh biến hình có thể ổn định những Tiếng Vọng vô chủ tại đây bằng Trường Thanh Âm của nó, ngăn chúng tan biến hay trở nên thù địch.</t>
         </is>
       </c>
     </row>
@@ -29031,7 +29031,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Chúng tôi trông cậy vào cậu để thu thập thêm Hòm Dư Âm, cung cấp năng lượng cho bức tranh. Tôi cũng sẽ để mắt tới những hiện tượng kỳ lạ của Echo và báo cậu ngay nếu có gì bất thường.</t>
+          <t>Chúng tôi trông cậy vào cậu để thu thập thêm Hòm Dư Âm, cung cấp năng lượng cho bức tranh. Tôi cũng sẽ để mắt tới những hiện tượng kỳ lạ của Tiếng Vọng và báo cậu ngay nếu có gì bất thường.</t>
         </is>
       </c>
     </row>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>{Male=Anh;Female=Chị} {PlayerName}, sao {Male=anh;Female=chị} lại có những suy nghĩ báng bổ như vậy? Thách thức uy quyền của Sentinel... ngay cả dân ngoại cũng có thể bị đưa đi hành hương vì điều đó!</t>
+          <t>{Male=Mr.;Female=Ms.} {PlayerName}, sao bạn lại có những suy nghĩ báng bổ như vậy? Thách thức uy quyền của Sentinel... ngay cả dân ngoại cũng có thể bị đưa đi hành hương vì điều đó!</t>
         </is>
       </c>
     </row>
@@ -29421,7 +29421,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Đây có vẻ là bản ghi lại lễ hội Carnevale cổ xưa. Không thấy bóng dáng Acolyte nào cả... Liệu có phải từ trước khi Dòng Sâu được thành lập không? Một phát hiện tuyệt vời đấy, {Male=ngài;Female=nữ} {PlayerName}!</t>
+          <t>Đây có vẻ là bản ghi lại lễ hội Carnevale cổ xưa. Không thấy bóng dáng Acolyte nào cả... Liệu có phải từ trước khi Dòng Sâu được thành lập không? Một phát hiện tuyệt vời đấy, {Male=Mr.;Female=Ms.} {PlayerName}!</t>
         </is>
       </c>
     </row>
@@ -29616,7 +29616,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Chương 2, Khổ 10 của Giáo Lý: "Dù tâm hồn run rẩy, ngươi không được bỏ rơi lòng thành kính. Dù tâm hồn run rẩy, ngươi không được bỏ rơi lòng thành kính..." Calm nào, bình tĩnh nào, bình tĩnh nào!</t>
+          <t>Chương 2, Khổ 10 của Giáo Lý: "Dù tâm hồn run rẩy, ngươi không được bỏ rơi lòng thành kính. Dù tâm hồn run rẩy, ngươi không được bỏ rơi lòng thành kính..." Bình tĩnh nào, bình tĩnh nào, bình tĩnh nào!</t>
         </is>
       </c>
     </row>
@@ -29746,7 +29746,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Sau Dark Tide hai mươi năm trước, Đức Giáo Hoàng Fenrico tuyên bố rằng sự khoan dung của Hội đối với sự hỗn loạn đã dẫn đến tai họa. Để đáp lại, ngài đã sửa đổi kinh thánh và kêu gọi tất cả tín đồ sống theo lời dạy đó mãi mãi.</t>
+          <t>Sau Thủy Triều Bóng Tối hai mươi năm trước, Đức Giáo Hoàng Fenrico tuyên bố rằng sự khoan dung của Hội đối với sự hỗn loạn đã dẫn đến tai họa. Để đáp lại, ngài đã sửa đổi kinh thánh và kêu gọi tất cả tín đồ sống theo lời dạy đó mãi mãi.</t>
         </is>
       </c>
     </row>
@@ -29811,7 +29811,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>{Male=Thưa anh;Female=Thưa chị} {PlayerName}, tôi không phải người thông minh nhất trong số đồng nghiệp, nhưng tôi hiểu ý {Male=anh;Female=chị} muốn nói. {Male=Anh;Female=Chị} là người tốt, điều đó tôi có thể thấy rõ.</t>
+          <t>{Male=Mr.;Female=Ms.} {PlayerName}, tôi không phải người thông minh nhất trong số đồng nghiệp, nhưng tôi hiểu ý bạn muốn nói. bạn là người tốt, điều đó tôi có thể thấy rõ.</t>
         </is>
       </c>
     </row>
@@ -29941,7 +29941,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>{Male=Anh;Female=Chị} {PlayerName}, {Male=anh;Female=chị} có sẵn lòng đánh bại con quái thú bên trong và mang về phần cuối của Dàn Hợp Xướng Nimbus không? Nó chắc chắn sẽ tôn vinh vinh quang của Sentinel.</t>
+          <t>{Male=Mr.;Female=Ms.} {PlayerName}, bạn có sẵn lòng đánh bại con quái thú bên trong và mang về phần cuối của Dàn Hợp Xướng Nimbus không? Nó chắc chắn sẽ tôn vinh vinh quang của Sentinel.</t>
         </is>
       </c>
     </row>
@@ -30006,7 +30006,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Cảm ơn {Male=anh;Female=chị} {PlayerName}! Tôi xin thề trước Lenore—cái tên mà Đức Thánh Primus ban cho—sẽ đền đáp ân tình này bằng cả tấm lòng.</t>
+          <t>Cảm ơn bạn {PlayerName}! Tôi xin thề trước Lenore—cái tên mà Đức Thánh Primus ban cho—sẽ đền đáp ân tình này bằng cả tấm lòng.</t>
         </is>
       </c>
     </row>
@@ -30071,7 +30071,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Haha, không sao đâu, {Male=anh;Female=chị} {PlayerName}! Như trong Chương 1, Khổ 9 của Giáo Lý Vực Sâu có viết: "Vệ Thần vĩ đại đã rải phước lành của Ngài lên Rinascita, đáp ứng đầy đủ nhu cầu của con dân Ngài."</t>
+          <t>Haha, không sao đâu, {Male=Mr.;Female=Ms.} {PlayerName}! Như trong Chương 1, Khổ 9 của Giáo Lý Vực Sâu có viết: "Vệ Thần vĩ đại đã rải phước lành của Ngài lên Rinascita, đáp ứng đầy đủ nhu cầu của con dân Ngài."</t>
         </is>
       </c>
     </row>
@@ -30136,7 +30136,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Nó gọi là Kho Archive Cấm Nhỏ. Ta có hai kho: một lớn, một nhỏ. Kho Archive Cấm Lớn là nơi cất giữ những cuốn sách, câu chuyện và tư tưởng nguy hiểm nhất. Chỉ những tín đồ trung thành nhất của Sentinel mới được phục vụ ở đó!</t>
+          <t>Nó gọi là Kho Lưu Trữ Cấm Nhỏ. Ta có hai kho: một lớn, một nhỏ. Kho Lưu Trữ Cấm Lớn là nơi cất giữ những cuốn sách, câu chuyện và tư tưởng nguy hiểm nhất. Chỉ những tín đồ trung thành nhất của Sentinel mới được phục vụ ở đó!</t>
         </is>
       </c>
     </row>
@@ -30201,7 +30201,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Đúng vậy, ta chính là Hiệu Trưởng Kho Archive Cấm Tiểu! Dù suốt tám năm qua, chỉ có một mình ta... Nhưng ta đã đọc và thuộc lòng bộ quy tắc ứng xử của Hiệu Trưởng không biết bao nhiêu lần rồi. Ta tự đặt mình vào những tiêu chuẩn cao nhất mà một Hiệu Trưởng có thể đạt được!</t>
+          <t>Đúng vậy, ta chính là Hiệu Trưởng Kho Lưu Trữ Cấm Tiểu! Dù suốt tám năm qua, chỉ có một mình ta... Nhưng ta đã đọc và thuộc lòng bộ quy tắc ứng xử của Hiệu Trưởng không biết bao nhiêu lần rồi. Ta tự đặt mình vào những tiêu chuẩn cao nhất mà một Hiệu Trưởng có thể đạt được!</t>
         </is>
       </c>
     </row>
@@ -30331,7 +30331,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Nhưng tớ phải làm điều này. Tớ đã làm việc ở Kho Archive Cấm Tiểu suốt tám năm dài đằng đẵng. Nếu cứ chần chừ thêm, Phoebe và mấy đứa kia sẽ vượt mặt tớ mất. Tớ phải làm gương cho chúng!</t>
+          <t>Nhưng tớ phải làm điều này. Tớ đã làm việc ở Kho Lưu Trữ Cấm Tiểu suốt tám năm dài đằng đẵng. Nếu cứ chần chừ thêm, Phoebe và mấy đứa kia sẽ vượt mặt tớ mất. Tớ phải làm gương cho chúng!</t>
         </is>
       </c>
     </row>
@@ -30591,7 +30591,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Tôi là Lenore, hiệu trưởng Kho Archive Cấm Thứ Yếu thuộc Dòng Trật Tự Deep. Nếu hôm nay tôi sống sót trở về, hãy đến tìm tôi tại Kho Archive Cấm Thứ Yếu. Tôi sẽ làm tất cả để đền đáp ơn cậu!</t>
+          <t>Tôi là Lenore, hiệu trưởng Kho Lưu Trữ Cấm Thứ Yếu thuộc Dòng Trật Tự Sâu Thẳm. Nếu hôm nay tôi sống sót trở về, hãy đến tìm tôi tại Kho Lưu Trữ Cấm Thứ Yếu. Tôi sẽ làm tất cả để đền đáp ơn cậu!</t>
         </is>
       </c>
     </row>
@@ -31111,7 +31111,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Haha, cậu lúc nào cũng có cách nói chuyện khéo léo. Kho Archive Cấm Địa nằm dưới lòng đất, làm gì có cảnh đẹp như thế này. Không, ta đến Thánh Đường Thủy Triều để hoàn tất thủ tục chuyển nhượng.</t>
+          <t>Haha, cậu lúc nào cũng có cách nói chuyện khéo léo. Kho Lưu Trữ Cấm Địa nằm dưới lòng đất, làm gì có cảnh đẹp như thế này. Không, ta đến Thánh Đường Thủy Triều để hoàn tất thủ tục chuyển nhượng.</t>
         </is>
       </c>
     </row>
@@ -31241,7 +31241,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>"Niềm tin chân chính khởi nguồn từ trái tim, và lời dẫn dắt của Sentinel vang lên qua giọng nói của ta. Từ đáy lòng, ta cảm ơn sự giúp đỡ của {Male=anh;Female=chị}, {Male=anh;Female=chị} {PlayerName}."</t>
+          <t>"Niềm tin chân chính khởi nguồn từ trái tim, và lời dẫn dắt của Sentinel vang lên qua giọng nói của ta. Từ đáy lòng, ta cảm ơn sự giúp đỡ của bạn, {PlayerName}."</t>
         </is>
       </c>
     </row>
@@ -31436,7 +31436,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>{Male=Anh;Female=Chị} {PlayerName}, {Male=anh;Female=chị} có biết về Thủy Triều Hắc Ám không? Đó là một tai họa từ trời cao, một vực thẳm nuốt chửng tất cả. Dòng thủy triều hủy diệt ấy đã cướp đi vô số gia đình, kể cả gia đình tôi.</t>
+          <t>{Male=Mr.;Female=Ms.} {PlayerName}, bạn có biết về Thủy Triều Hắc Ám không? Đó là một tai họa từ trời cao, một vực thẳm nuốt chửng tất cả. Dòng thủy triều hủy diệt ấy đã cướp đi vô số gia đình, kể cả gia đình tôi.</t>
         </is>
       </c>
     </row>
@@ -31566,7 +31566,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Khoan, trước khi tiếp tục... Theo nghiên cứu của tôi, cách đúng để thưởng thức Nimbus Chorale là phát đồng thời nhiều phần nhạc chồng lên nhau!</t>
+          <t>Đợi đã, trước khi tiếp tục... Theo nghiên cứu của tôi, cách đúng để thưởng thức Nimbus Chorale là phát đồng thời nhiều phần nhạc chồng lên nhau!</t>
         </is>
       </c>
     </row>
@@ -31963,10 +31963,10 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Hóa ra những con Plushie kia là Echoes bị bỏ rơi, và tất cả những gì chúng muốn chỉ là được đoàn tụ với chủ nhân.
+          <t>Hóa ra những con Plushie kia là Echo bị bỏ rơi, và tất cả những gì chúng muốn chỉ là được đoàn tụ với chủ nhân.
 Dù đã đến được hòn đảo hoang tàn này, chúng vẫn không tìm thấy chủ nhân của mình.
 Thay vào đó, chúng tìm thấy niềm an ủi trong những tần số cảm xúc vương vấn trên đồ vật, rồi bắt đầu ghép nối những "ngôi nhà" từ những mảnh ký ức vụn vỡ. Đó là cách chúng phát hiện ra "ngôi sao".
-Roccia tin rằng cả con người lẫn Echoes đều cần một nơi để trở về. Bạn đề nghị đưa những con Plushie về cùng với Fool's Troupe.</t>
+Roccia tin rằng cả con người lẫn Echo đều cần một nơi để trở về. Bạn đề nghị đưa những con Plushie về cùng với Fool's Troupe.</t>
         </is>
       </c>
     </row>
@@ -32163,7 +32163,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Tôi... tôi thực sự lo lắng khi gia nhập Pioneer Association. Có quá nhiều điều chưa biết phía trước! Nhưng tôi cũng lo cho hai đứa em trai của mình. Vì thế tôi cần Mây Nightmare để rèn luyện ý chí!</t>
+          <t>Tôi... tôi thực sự lo lắng khi gia nhập Hiệp Hội Tiên Phong. Có quá nhiều điều chưa biết phía trước! Nhưng tôi cũng lo cho hai đứa em trai của mình. Vì thế tôi cần Mây Ác Mộng để rèn luyện ý chí!</t>
         </is>
       </c>
     </row>
@@ -33006,7 +33006,7 @@
           <t>Ta tìm thấy vài rương chứa đồ rõ ràng không thuộc về Kho Tàng Âm Thanh. Chúng có lẽ bị bỏ lại trong một lần chuyển hàng trước đó.
 Không có bất kỳ ghi chép nào liên quan đến những chiếc rương này trong Kho Lưu Trữ, nên quyền sở hữu của chúng chưa được xác minh. Kho Lưu Trữ Kim Loại Quý và Tác Phẩm Nghệ Thuật cũng từ chối nhận chúng.
 Kho Tàng Âm Thanh không cần những vật liệu này, và chúng chỉ chiếm chỗ ở đây… nhưng hiện tại, không còn lựa chọn nào khác ngoài việc tiếp tục lưu giữ chúng ở đây.
-(Dưới ghi chú, bằng một Dodget chữ khác vội vàng viết)
+(Dưới ghi chú, bằng một nét chữ khác vội vàng viết)
 Đây không phải tài sản của Kho Lưu Trữ. Ai muốn thì cứ lấy đi.</t>
         </is>
       </c>
